--- a/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1144,7 +1144,7 @@
       <c r="A4" s="0" t="inlineStr"/>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>TagCategory</t>
+          <t>TagEffectType</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -1160,13 +1160,13 @@
       <c r="E4" s="0" t="inlineStr"/>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>标签分类：固有/唯一A/唯一B</t>
+          <t>标签效果类型</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr"/>
       <c r="H4" s="0" t="inlineStr">
         <is>
-          <t>Inherent</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I4" s="0" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
       <c r="G5" s="0" t="inlineStr"/>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t>UniqueA</t>
+          <t>AddFlat</t>
         </is>
       </c>
       <c r="I5" s="0" t="inlineStr"/>
@@ -1206,7 +1206,7 @@
       <c r="G6" s="0" t="inlineStr"/>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t>UniqueB</t>
+          <t>AddMult</t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr"/>
@@ -1218,36 +1218,20 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr"/>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>TagEffectType</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
+      <c r="B7" s="0" t="inlineStr"/>
+      <c r="C7" s="0" t="inlineStr"/>
+      <c r="D7" s="0" t="inlineStr"/>
       <c r="E7" s="0" t="inlineStr"/>
-      <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t>标签效果类型</t>
-        </is>
-      </c>
+      <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>PerAdjacentDish</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr"/>
       <c r="J7" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" s="0" t="inlineStr"/>
       <c r="L7" s="0" t="inlineStr"/>
@@ -1262,12 +1246,12 @@
       <c r="G8" s="0" t="inlineStr"/>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t>AddFlat</t>
+          <t>PerEmptyCell</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr"/>
       <c r="J8" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K8" s="0" t="inlineStr"/>
       <c r="L8" s="0" t="inlineStr"/>
@@ -1282,12 +1266,12 @@
       <c r="G9" s="0" t="inlineStr"/>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t>AddMult</t>
+          <t>PerOccupiedCell</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr"/>
       <c r="J9" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K9" s="0" t="inlineStr"/>
       <c r="L9" s="0" t="inlineStr"/>
@@ -1302,75 +1286,15 @@
       <c r="G10" s="0" t="inlineStr"/>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t>PerAdjacentDish</t>
+          <t>PerDishOnBoard</t>
         </is>
       </c>
       <c r="I10" s="0" t="inlineStr"/>
       <c r="J10" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K10" s="0" t="inlineStr"/>
       <c r="L10" s="0" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr"/>
-      <c r="B11" s="0" t="inlineStr"/>
-      <c r="C11" s="0" t="inlineStr"/>
-      <c r="D11" s="0" t="inlineStr"/>
-      <c r="E11" s="0" t="inlineStr"/>
-      <c r="F11" s="0" t="inlineStr"/>
-      <c r="G11" s="0" t="inlineStr"/>
-      <c r="H11" s="0" t="inlineStr">
-        <is>
-          <t>PerEmptyCell</t>
-        </is>
-      </c>
-      <c r="I11" s="0" t="inlineStr"/>
-      <c r="J11" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" s="0" t="inlineStr"/>
-      <c r="L11" s="0" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr"/>
-      <c r="B12" s="0" t="inlineStr"/>
-      <c r="C12" s="0" t="inlineStr"/>
-      <c r="D12" s="0" t="inlineStr"/>
-      <c r="E12" s="0" t="inlineStr"/>
-      <c r="F12" s="0" t="inlineStr"/>
-      <c r="G12" s="0" t="inlineStr"/>
-      <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t>PerOccupiedCell</t>
-        </is>
-      </c>
-      <c r="I12" s="0" t="inlineStr"/>
-      <c r="J12" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" s="0" t="inlineStr"/>
-      <c r="L12" s="0" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="inlineStr"/>
-      <c r="B13" s="0" t="inlineStr"/>
-      <c r="C13" s="0" t="inlineStr"/>
-      <c r="D13" s="0" t="inlineStr"/>
-      <c r="E13" s="0" t="inlineStr"/>
-      <c r="F13" s="0" t="inlineStr"/>
-      <c r="G13" s="0" t="inlineStr"/>
-      <c r="H13" s="0" t="inlineStr">
-        <is>
-          <t>PerDishOnBoard</t>
-        </is>
-      </c>
-      <c r="I13" s="0" t="inlineStr"/>
-      <c r="J13" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="K13" s="0" t="inlineStr"/>
-      <c r="L13" s="0" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1296,6 +1296,928 @@
       <c r="K10" s="0" t="inlineStr"/>
       <c r="L10" s="0" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SkillConditionType</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>技能前提类型</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>无前提，恒触发一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PositionFilled</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>作用域存在格是否全被占满(闸门)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>EmptyCell</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>作用域内空格数</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>本菜是否处于棋盘边缘(闸门)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>DishCount</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>作用域内菜数</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>DishSize</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>作用域内占格数比较阈值的菜数</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ServeOrder</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>上菜顺序在前/后的菜数</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SameDish</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>作用域内同BaseId的菜数</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SameKindInRun</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>本局已结算过本种的次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SameKindInMeal</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>本次品鉴本种数量/已结算次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TagCount</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>本菜标签数</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ShapeMatch</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>作用域内形状匹配condParam的菜数</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>RecipeCount</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>菜谱内菜数比较阈值(闸门)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>LayerCount</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>本菜当前层数</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SkillScope</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>技能作用域</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>本菜自身</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>相邻菜</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>本行</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>本列</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>全部菜</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>空格</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>边缘</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>上菜顺序在前</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>上菜顺序在后</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Recipe</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>菜谱</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CompareOp</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>比较符</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>不比较</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Gte</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>大于等于</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Lte</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>小于等于</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Eq</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>等于</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Gt</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>大于</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Lt</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>小于</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CountMode</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>计数模式</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>每有1个:count=raw</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>达到阈值:闸门</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>布尔条件:闸门</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CountUnit</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>计数单位</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>按实例(个)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kinds</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>按BaseId去重(种)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SkillActionType</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>技能行为类型</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>无行为</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>目标加法区+X*count</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>AddMult</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>目标乘区*X(叠count次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>TransferScore</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>来源加法分按比例转移给目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ExtraSettlement</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>目标额外结算X次</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>TransferSkills</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>来源技能传递给目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>AddLayer</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>层数+X(mult时*X)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ConsumeLayer</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>层数-X</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>GrantGold</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>获得X*count金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SkillTrigger</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>技能触发时机</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>结算时</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>OnServe</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>上菜时</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1297,922 +1297,939 @@
       <c r="L10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>SkillConditionType</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>技能前提类型</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t>无前提，恒触发一次</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>PositionFilled</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
         <is>
           <t>作用域存在格是否全被占满(闸门)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>EmptyCell</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t>作用域内空格数</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
         <is>
           <t>本菜是否处于棋盘边缘(闸门)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>DishCount</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t>作用域内菜数</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>DishSize</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="0" t="inlineStr">
         <is>
           <t>作用域内占格数比较阈值的菜数</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>ServeOrder</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
         <is>
           <t>上菜顺序在前/后的菜数</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>SameDish</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="0" t="inlineStr">
         <is>
           <t>作用域内同BaseId的菜数</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>SameKindInRun</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>本局已结算过本种的次数</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>SameKindInMeal</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="0" t="inlineStr">
         <is>
           <t>本次品鉴本种数量/已结算次数</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>TagCount</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="0" t="inlineStr">
         <is>
           <t>本菜标签数</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>ShapeMatch</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="0" t="inlineStr">
         <is>
           <t>作用域内形状匹配condParam的菜数</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>RecipeCount</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="0" t="inlineStr">
         <is>
           <t>菜谱内菜数比较阈值(闸门)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="0" t="inlineStr">
         <is>
           <t>LayerCount</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="0" t="inlineStr">
         <is>
           <t>本菜当前层数</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>OccupiedCell</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="inlineStr">
+        <is>
+          <t>本菜占用格数</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>SkillScope</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" s="0" t="inlineStr">
         <is>
           <t>技能作用域</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J26" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K26" s="0" t="inlineStr">
         <is>
           <t>本菜自身</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="H26" t="inlineStr">
+    <row r="27">
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>Adjacent</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J27" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K27" s="0" t="inlineStr">
         <is>
           <t>相邻菜</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="H27" t="inlineStr">
+    <row r="28">
+      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t>本行</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="H28" t="inlineStr">
+    <row r="29">
+      <c r="H29" s="0" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J29" s="0" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K29" s="0" t="inlineStr">
         <is>
           <t>本列</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="H29" t="inlineStr">
+    <row r="30">
+      <c r="H30" s="0" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K30" s="0" t="inlineStr">
         <is>
           <t>全部菜</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="H30" t="inlineStr">
+    <row r="31">
+      <c r="H31" s="0" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J31" s="0" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K31" s="0" t="inlineStr">
         <is>
           <t>空格</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="H31" t="inlineStr">
+    <row r="32">
+      <c r="H32" s="0" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J32" s="0" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K32" s="0" t="inlineStr">
         <is>
           <t>边缘</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="H32" t="inlineStr">
+    <row r="33">
+      <c r="H33" s="0" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J33" s="0" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K33" s="0" t="inlineStr">
         <is>
           <t>上菜顺序在前</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="H33" t="inlineStr">
+    <row r="34">
+      <c r="H34" s="0" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J34" s="0" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K34" s="0" t="inlineStr">
         <is>
           <t>上菜顺序在后</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="H34" t="inlineStr">
+    <row r="35">
+      <c r="H35" s="0" t="inlineStr">
         <is>
           <t>Recipe</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J35" s="0" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K35" s="0" t="inlineStr">
         <is>
           <t>菜谱</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>CompareOp</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" s="0" t="inlineStr">
         <is>
           <t>比较符</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J36" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K36" s="0" t="inlineStr">
         <is>
           <t>不比较</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="H36" t="inlineStr">
+    <row r="37">
+      <c r="H37" s="0" t="inlineStr">
         <is>
           <t>Gte</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J37" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K37" s="0" t="inlineStr">
         <is>
           <t>大于等于</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="H37" t="inlineStr">
+    <row r="38">
+      <c r="H38" s="0" t="inlineStr">
         <is>
           <t>Lte</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J38" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K38" s="0" t="inlineStr">
         <is>
           <t>小于等于</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="H38" t="inlineStr">
+    <row r="39">
+      <c r="H39" s="0" t="inlineStr">
         <is>
           <t>Eq</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J39" s="0" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K39" s="0" t="inlineStr">
         <is>
           <t>等于</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="H39" t="inlineStr">
+    <row r="40">
+      <c r="H40" s="0" t="inlineStr">
         <is>
           <t>Gt</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J40" s="0" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K40" s="0" t="inlineStr">
         <is>
           <t>大于</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="H40" t="inlineStr">
+    <row r="41">
+      <c r="H41" s="0" t="inlineStr">
         <is>
           <t>Lt</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J41" s="0" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K41" s="0" t="inlineStr">
         <is>
           <t>小于</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>CountMode</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" s="0" t="inlineStr">
         <is>
           <t>计数模式</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" s="0" t="inlineStr">
         <is>
           <t>Per</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K42" s="0" t="inlineStr">
         <is>
           <t>每有1个:count=raw</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="H42" t="inlineStr">
+    <row r="43">
+      <c r="H43" s="0" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J43" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K43" s="0" t="inlineStr">
         <is>
           <t>达到阈值:闸门</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="H43" t="inlineStr">
+    <row r="44">
+      <c r="H44" s="0" t="inlineStr">
         <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J44" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K44" s="0" t="inlineStr">
         <is>
           <t>布尔条件:闸门</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>CountUnit</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" s="0" t="inlineStr">
         <is>
           <t>计数单位</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H45" s="0" t="inlineStr">
         <is>
           <t>Instances</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J45" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K45" s="0" t="inlineStr">
         <is>
           <t>按实例(个)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="H45" t="inlineStr">
+    <row r="46">
+      <c r="H46" s="0" t="inlineStr">
         <is>
           <t>Kinds</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J46" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K46" s="0" t="inlineStr">
         <is>
           <t>按BaseId去重(种)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>SkillActionType</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" s="0" t="inlineStr">
         <is>
           <t>技能行为类型</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H47" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J47" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K47" s="0" t="inlineStr">
         <is>
           <t>无行为</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="H47" t="inlineStr">
+    <row r="48">
+      <c r="H48" s="0" t="inlineStr">
         <is>
           <t>AddFlat</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J48" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K48" s="0" t="inlineStr">
         <is>
           <t>目标加法区+X*count</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="H48" t="inlineStr">
+    <row r="49">
+      <c r="H49" s="0" t="inlineStr">
         <is>
           <t>AddMult</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J49" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K49" s="0" t="inlineStr">
         <is>
           <t>目标乘区*X(叠count次)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="H49" t="inlineStr">
+    <row r="50">
+      <c r="H50" s="0" t="inlineStr">
         <is>
           <t>TransferScore</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J50" s="0" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K50" s="0" t="inlineStr">
         <is>
           <t>来源加法分按比例转移给目标</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="H50" t="inlineStr">
+    <row r="51">
+      <c r="H51" s="0" t="inlineStr">
         <is>
           <t>ExtraSettlement</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J51" s="0" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K51" s="0" t="inlineStr">
         <is>
           <t>目标额外结算X次</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="H51" t="inlineStr">
+    <row r="52">
+      <c r="H52" s="0" t="inlineStr">
         <is>
           <t>TransferSkills</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J52" s="0" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K52" s="0" t="inlineStr">
         <is>
           <t>来源技能传递给目标</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="H52" t="inlineStr">
+    <row r="53">
+      <c r="H53" s="0" t="inlineStr">
         <is>
           <t>AddLayer</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J53" s="0" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K53" s="0" t="inlineStr">
         <is>
           <t>层数+X(mult时*X)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="H53" t="inlineStr">
+    <row r="54">
+      <c r="H54" s="0" t="inlineStr">
         <is>
           <t>ConsumeLayer</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J54" s="0" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K54" s="0" t="inlineStr">
         <is>
           <t>层数-X</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="H54" t="inlineStr">
+    <row r="55">
+      <c r="H55" s="0" t="inlineStr">
         <is>
           <t>GrantGold</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J55" s="0" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K55" s="0" t="inlineStr">
         <is>
           <t>获得X*count金币</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>SkillTrigger</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" s="0" t="inlineStr">
         <is>
           <t>技能触发时机</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" s="0" t="inlineStr">
         <is>
           <t>OnSettle</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J56" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K56" s="0" t="inlineStr">
         <is>
           <t>结算时</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="H56" t="inlineStr">
+    <row r="57">
+      <c r="H57" s="0" t="inlineStr">
         <is>
           <t>OnServe</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J57" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K57" s="0" t="inlineStr">
         <is>
           <t>上菜时</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1572,392 +1572,372 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="0" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CategoryCount</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>作用域内指定分类(condParam)的菜数</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SkillTypeCount</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>作用域内带某行为类技能(condParam)的菜数</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>SkillScope</t>
         </is>
       </c>
-      <c r="C26" s="0" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D26" s="0" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F26" s="0" t="inlineStr">
+      <c r="F28" s="0" t="inlineStr">
         <is>
           <t>技能作用域</t>
         </is>
       </c>
-      <c r="H26" s="0" t="inlineStr">
+      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="J26" s="0" t="inlineStr">
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K26" s="0" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t>本菜自身</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="H27" s="0" t="inlineStr">
-        <is>
-          <t>Adjacent</t>
-        </is>
-      </c>
-      <c r="J27" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" s="0" t="inlineStr">
-        <is>
-          <t>相邻菜</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="H28" s="0" t="inlineStr">
-        <is>
-          <t>Row</t>
-        </is>
-      </c>
-      <c r="J28" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" s="0" t="inlineStr">
-        <is>
-          <t>本行</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>Column</t>
+          <t>Adjacent</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t>本列</t>
+          <t>相邻菜</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Row</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K30" s="0" t="inlineStr">
         <is>
-          <t>全部菜</t>
+          <t>本行</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>Empty</t>
+          <t>Column</t>
         </is>
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K31" s="0" t="inlineStr">
         <is>
-          <t>空格</t>
+          <t>本列</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>All</t>
         </is>
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t>边缘</t>
+          <t>全部菜</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Empty</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t>上菜顺序在前</t>
+          <t>空格</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="H34" s="0" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t>上菜顺序在后</t>
+          <t>边缘</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t>Recipe</t>
+          <t>Before</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t>菜谱</t>
+          <t>上菜顺序在前</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="0" t="inlineStr">
-        <is>
-          <t>CompareOp</t>
-        </is>
-      </c>
-      <c r="C36" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D36" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F36" s="0" t="inlineStr">
-        <is>
-          <t>比较符</t>
-        </is>
-      </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>After</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t>不比较</t>
+          <t>上菜顺序在后</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>Gte</t>
+          <t>Recipe</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t>大于等于</t>
+          <t>菜谱</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="H38" s="0" t="inlineStr">
-        <is>
-          <t>Lte</t>
-        </is>
-      </c>
-      <c r="J38" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" s="0" t="inlineStr">
-        <is>
-          <t>小于等于</t>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>指定分类(condParam/actionParam)的菜</t>
         </is>
       </c>
     </row>
     <row r="39">
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>CompareOp</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="inlineStr">
+        <is>
+          <t>比较符</t>
+        </is>
+      </c>
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t>Eq</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K39" s="0" t="inlineStr">
         <is>
-          <t>等于</t>
+          <t>不比较</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>Gt</t>
+          <t>Gte</t>
         </is>
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" s="0" t="inlineStr">
         <is>
-          <t>大于</t>
+          <t>大于等于</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>Lt</t>
+          <t>Lte</t>
         </is>
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" s="0" t="inlineStr">
         <is>
-          <t>小于</t>
+          <t>小于等于</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="0" t="inlineStr">
-        <is>
-          <t>CountMode</t>
-        </is>
-      </c>
-      <c r="C42" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D42" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F42" s="0" t="inlineStr">
-        <is>
-          <t>计数模式</t>
-        </is>
-      </c>
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t>Per</t>
+          <t>Eq</t>
         </is>
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K42" s="0" t="inlineStr">
         <is>
-          <t>每有1个:count=raw</t>
+          <t>等于</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>Reach</t>
+          <t>Gt</t>
         </is>
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K43" s="0" t="inlineStr">
         <is>
-          <t>达到阈值:闸门</t>
+          <t>大于</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Lt</t>
         </is>
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K44" s="0" t="inlineStr">
         <is>
-          <t>布尔条件:闸门</t>
+          <t>小于</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>CountUnit</t>
+          <t>CountMode</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -1972,12 +1952,12 @@
       </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
-          <t>计数单位</t>
+          <t>计数模式</t>
         </is>
       </c>
       <c r="H45" s="0" t="inlineStr">
         <is>
-          <t>Instances</t>
+          <t>Per</t>
         </is>
       </c>
       <c r="J45" s="0" t="inlineStr">
@@ -1987,14 +1967,14 @@
       </c>
       <c r="K45" s="0" t="inlineStr">
         <is>
-          <t>按实例(个)</t>
+          <t>每有1个:count=raw</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t>Kinds</t>
+          <t>Reach</t>
         </is>
       </c>
       <c r="J46" s="0" t="inlineStr">
@@ -2004,232 +1984,405 @@
       </c>
       <c r="K46" s="0" t="inlineStr">
         <is>
-          <t>按BaseId去重(种)</t>
+          <t>达到阈值:闸门</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="0" t="inlineStr">
-        <is>
-          <t>SkillActionType</t>
-        </is>
-      </c>
-      <c r="C47" s="0" t="inlineStr">
+      <c r="H47" s="0" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K47" s="0" t="inlineStr">
+        <is>
+          <t>布尔条件:闸门</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>CountUnit</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D47" s="0" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F47" s="0" t="inlineStr">
-        <is>
-          <t>技能行为类型</t>
-        </is>
-      </c>
-      <c r="H47" s="0" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J47" s="0" t="inlineStr">
+      <c r="F48" s="0" t="inlineStr">
+        <is>
+          <t>计数单位</t>
+        </is>
+      </c>
+      <c r="H48" s="0" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K47" s="0" t="inlineStr">
-        <is>
-          <t>无行为</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="H48" s="0" t="inlineStr">
-        <is>
-          <t>AddFlat</t>
-        </is>
-      </c>
-      <c r="J48" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K48" s="0" t="inlineStr">
         <is>
-          <t>目标加法区+X*count</t>
+          <t>按实例(个)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="H49" s="0" t="inlineStr">
         <is>
-          <t>AddMult</t>
+          <t>Kinds</t>
         </is>
       </c>
       <c r="J49" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K49" s="0" t="inlineStr">
         <is>
-          <t>目标乘区*X(叠count次)</t>
+          <t>按BaseId去重(种)</t>
         </is>
       </c>
     </row>
     <row r="50">
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>SkillActionType</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F50" s="0" t="inlineStr">
+        <is>
+          <t>技能行为类型</t>
+        </is>
+      </c>
       <c r="H50" s="0" t="inlineStr">
         <is>
-          <t>TransferScore</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J50" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K50" s="0" t="inlineStr">
         <is>
-          <t>来源加法分按比例转移给目标</t>
+          <t>无行为</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="H51" s="0" t="inlineStr">
         <is>
-          <t>ExtraSettlement</t>
+          <t>AddFlat</t>
         </is>
       </c>
       <c r="J51" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" s="0" t="inlineStr">
         <is>
-          <t>目标额外结算X次</t>
+          <t>目标加法区+X*count</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="H52" s="0" t="inlineStr">
         <is>
-          <t>TransferSkills</t>
+          <t>AddMult</t>
         </is>
       </c>
       <c r="J52" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K52" s="0" t="inlineStr">
         <is>
-          <t>来源技能传递给目标</t>
+          <t>目标乘区*X(叠count次)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="H53" s="0" t="inlineStr">
         <is>
-          <t>AddLayer</t>
+          <t>TransferScore</t>
         </is>
       </c>
       <c r="J53" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K53" s="0" t="inlineStr">
         <is>
-          <t>层数+X(mult时*X)</t>
+          <t>来源加法分按比例转移给目标</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="H54" s="0" t="inlineStr">
         <is>
-          <t>ConsumeLayer</t>
+          <t>ExtraSettlement</t>
         </is>
       </c>
       <c r="J54" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K54" s="0" t="inlineStr">
         <is>
-          <t>层数-X</t>
+          <t>目标额外结算X次</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="H55" s="0" t="inlineStr">
         <is>
-          <t>GrantGold</t>
+          <t>TransferSkills</t>
         </is>
       </c>
       <c r="J55" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K55" s="0" t="inlineStr">
         <is>
-          <t>获得X*count金币</t>
+          <t>来源技能传递给目标</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="0" t="inlineStr">
-        <is>
-          <t>SkillTrigger</t>
-        </is>
-      </c>
-      <c r="C56" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D56" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F56" s="0" t="inlineStr">
-        <is>
-          <t>技能触发时机</t>
-        </is>
-      </c>
       <c r="H56" s="0" t="inlineStr">
         <is>
-          <t>OnSettle</t>
+          <t>AddLayer</t>
         </is>
       </c>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K56" s="0" t="inlineStr">
         <is>
-          <t>结算时</t>
+          <t>层数+X(mult时*X)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="H57" s="0" t="inlineStr">
         <is>
+          <t>ConsumeLayer</t>
+        </is>
+      </c>
+      <c r="J57" s="0" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K57" s="0" t="inlineStr">
+        <is>
+          <t>层数-X</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t>GrantGold</t>
+        </is>
+      </c>
+      <c r="J58" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K58" s="0" t="inlineStr">
+        <is>
+          <t>获得X*count金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>AddMultFlat</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>目标乘区+X*count(加法叠加到倍率)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>PermanentAddFlat</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>目标永久加法+X(跨结算持久)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>PermanentAddMult</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>目标永久乘区*X(跨结算持久)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>AddCountAs</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>目标"视为食物数"+X*count</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>CopySkill</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>从来源作用域随机复制actionCount个技能给目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>TempCopyDish</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>临时复制目标菜到空格(本次品鉴)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>SkillTrigger</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D65" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F65" s="0" t="inlineStr">
+        <is>
+          <t>技能触发时机</t>
+        </is>
+      </c>
+      <c r="H65" s="0" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="J65" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K65" s="0" t="inlineStr">
+        <is>
+          <t>结算时</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="H66" s="0" t="inlineStr">
+        <is>
           <t>OnServe</t>
         </is>
       </c>
-      <c r="J57" s="0" t="inlineStr">
+      <c r="J66" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K57" s="0" t="inlineStr">
+      <c r="K66" s="0" t="inlineStr">
         <is>
           <t>上菜时</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1572,34 +1572,34 @@
       </c>
     </row>
     <row r="26">
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>CategoryCount</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="0" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="0" t="inlineStr">
         <is>
           <t>作用域内指定分类(condParam)的菜数</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>SkillTypeCount</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="0" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="0" t="inlineStr">
         <is>
           <t>作用域内带某行为类技能(condParam)的菜数</t>
         </is>
@@ -1796,17 +1796,17 @@
       </c>
     </row>
     <row r="38">
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="0" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="0" t="inlineStr">
         <is>
           <t>指定分类(condParam/actionParam)的菜</t>
         </is>
@@ -2233,156 +2233,176 @@
       </c>
     </row>
     <row r="59">
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="0" t="inlineStr">
         <is>
           <t>AddMultFlat</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="0" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" s="0" t="inlineStr">
         <is>
           <t>目标乘区+X*count(加法叠加到倍率)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="0" t="inlineStr">
         <is>
           <t>PermanentAddFlat</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J60" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K60" s="0" t="inlineStr">
         <is>
           <t>目标永久加法+X(跨结算持久)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="0" t="inlineStr">
         <is>
           <t>PermanentAddMult</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J61" s="0" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K61" s="0" t="inlineStr">
         <is>
           <t>目标永久乘区*X(跨结算持久)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="0" t="inlineStr">
         <is>
           <t>AddCountAs</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" s="0" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K62" s="0" t="inlineStr">
         <is>
           <t>目标"视为食物数"+X*count</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="0" t="inlineStr">
         <is>
           <t>CopySkill</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J63" s="0" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K63" s="0" t="inlineStr">
         <is>
           <t>从来源作用域随机复制actionCount个技能给目标</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="0" t="inlineStr">
         <is>
           <t>TempCopyDish</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J64" s="0" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K64" s="0" t="inlineStr">
         <is>
           <t>临时复制目标菜到空格(本次品鉴)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="0" t="inlineStr">
+      <c r="E65" s="0" t="n"/>
+      <c r="F65" s="0" t="n"/>
+      <c r="G65" s="0" t="n"/>
+      <c r="H65" s="0" t="inlineStr">
+        <is>
+          <t>TriggerSweetTransfer</t>
+        </is>
+      </c>
+      <c r="J65" s="0" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K65" s="0" t="inlineStr">
+        <is>
+          <t>触发作用域内食物各执行一次自身甜蜜传递</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>SkillTrigger</t>
         </is>
       </c>
-      <c r="C65" s="0" t="inlineStr">
+      <c r="C66" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D65" s="0" t="inlineStr">
+      <c r="D66" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F65" s="0" t="inlineStr">
+      <c r="F66" s="0" t="inlineStr">
         <is>
           <t>技能触发时机</t>
         </is>
       </c>
-      <c r="H65" s="0" t="inlineStr">
+      <c r="H66" s="0" t="inlineStr">
         <is>
           <t>OnSettle</t>
         </is>
       </c>
-      <c r="J65" s="0" t="inlineStr">
+      <c r="J66" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K65" s="0" t="inlineStr">
+      <c r="K66" s="0" t="inlineStr">
         <is>
           <t>结算时</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="H66" s="0" t="inlineStr">
+    <row r="67">
+      <c r="H67" s="0" t="inlineStr">
         <is>
           <t>OnServe</t>
         </is>
       </c>
-      <c r="J66" s="0" t="inlineStr">
+      <c r="J67" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K66" s="0" t="inlineStr">
+      <c r="K67" s="0" t="inlineStr">
         <is>
           <t>上菜时</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1813,596 +1813,613 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="0" t="inlineStr">
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K39" s="0" t="inlineStr">
+        <is>
+          <t>周围菜(共边相邻+对角相邻)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>CompareOp</t>
         </is>
       </c>
-      <c r="C39" s="0" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D39" s="0" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F39" s="0" t="inlineStr">
+      <c r="F40" s="0" t="inlineStr">
         <is>
           <t>比较符</t>
         </is>
       </c>
-      <c r="H39" s="0" t="inlineStr">
+      <c r="H40" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J39" s="0" t="inlineStr">
+      <c r="J40" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K39" s="0" t="inlineStr">
+      <c r="K40" s="0" t="inlineStr">
         <is>
           <t>不比较</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="H40" s="0" t="inlineStr">
-        <is>
-          <t>Gte</t>
-        </is>
-      </c>
-      <c r="J40" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" s="0" t="inlineStr">
-        <is>
-          <t>大于等于</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>Lte</t>
+          <t>Gte</t>
         </is>
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" s="0" t="inlineStr">
         <is>
-          <t>小于等于</t>
+          <t>大于等于</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t>Eq</t>
+          <t>Lte</t>
         </is>
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K42" s="0" t="inlineStr">
         <is>
-          <t>等于</t>
+          <t>小于等于</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>Gt</t>
+          <t>Eq</t>
         </is>
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K43" s="0" t="inlineStr">
         <is>
-          <t>大于</t>
+          <t>等于</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="H44" s="0" t="inlineStr">
         <is>
+          <t>Gt</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K44" s="0" t="inlineStr">
+        <is>
+          <t>大于</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45" s="0" t="inlineStr">
+        <is>
           <t>Lt</t>
         </is>
       </c>
-      <c r="J44" s="0" t="inlineStr">
+      <c r="J45" s="0" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K44" s="0" t="inlineStr">
+      <c r="K45" s="0" t="inlineStr">
         <is>
           <t>小于</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="0" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>CountMode</t>
         </is>
       </c>
-      <c r="C45" s="0" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D45" s="0" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F45" s="0" t="inlineStr">
+      <c r="F46" s="0" t="inlineStr">
         <is>
           <t>计数模式</t>
         </is>
       </c>
-      <c r="H45" s="0" t="inlineStr">
+      <c r="H46" s="0" t="inlineStr">
         <is>
           <t>Per</t>
         </is>
       </c>
-      <c r="J45" s="0" t="inlineStr">
+      <c r="J46" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K45" s="0" t="inlineStr">
+      <c r="K46" s="0" t="inlineStr">
         <is>
           <t>每有1个:count=raw</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="H46" s="0" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="J46" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" s="0" t="inlineStr">
-        <is>
-          <t>达到阈值:闸门</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="H47" s="0" t="inlineStr">
         <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" s="0" t="inlineStr">
+        <is>
+          <t>达到阈值:闸门</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="H48" s="0" t="inlineStr">
+        <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="J47" s="0" t="inlineStr">
+      <c r="J48" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K47" s="0" t="inlineStr">
+      <c r="K48" s="0" t="inlineStr">
         <is>
           <t>布尔条件:闸门</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="0" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>CountUnit</t>
         </is>
       </c>
-      <c r="C48" s="0" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D48" s="0" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F48" s="0" t="inlineStr">
+      <c r="F49" s="0" t="inlineStr">
         <is>
           <t>计数单位</t>
         </is>
       </c>
-      <c r="H48" s="0" t="inlineStr">
+      <c r="H49" s="0" t="inlineStr">
         <is>
           <t>Instances</t>
         </is>
       </c>
-      <c r="J48" s="0" t="inlineStr">
+      <c r="J49" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K48" s="0" t="inlineStr">
+      <c r="K49" s="0" t="inlineStr">
         <is>
           <t>按实例(个)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="H49" s="0" t="inlineStr">
+    <row r="50">
+      <c r="H50" s="0" t="inlineStr">
         <is>
           <t>Kinds</t>
         </is>
       </c>
-      <c r="J49" s="0" t="inlineStr">
+      <c r="J50" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K49" s="0" t="inlineStr">
+      <c r="K50" s="0" t="inlineStr">
         <is>
           <t>按BaseId去重(种)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="0" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>SkillActionType</t>
         </is>
       </c>
-      <c r="C50" s="0" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D50" s="0" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F50" s="0" t="inlineStr">
+      <c r="F51" s="0" t="inlineStr">
         <is>
           <t>技能行为类型</t>
         </is>
       </c>
-      <c r="H50" s="0" t="inlineStr">
+      <c r="H51" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J50" s="0" t="inlineStr">
+      <c r="J51" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K50" s="0" t="inlineStr">
+      <c r="K51" s="0" t="inlineStr">
         <is>
           <t>无行为</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="H51" s="0" t="inlineStr">
-        <is>
-          <t>AddFlat</t>
-        </is>
-      </c>
-      <c r="J51" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" s="0" t="inlineStr">
-        <is>
-          <t>目标加法区+X*count</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="H52" s="0" t="inlineStr">
         <is>
-          <t>AddMult</t>
+          <t>AddFlat</t>
         </is>
       </c>
       <c r="J52" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" s="0" t="inlineStr">
         <is>
-          <t>目标乘区*X(叠count次)</t>
+          <t>目标加法区+X*count</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="H53" s="0" t="inlineStr">
         <is>
-          <t>TransferScore</t>
+          <t>AddMult</t>
         </is>
       </c>
       <c r="J53" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K53" s="0" t="inlineStr">
         <is>
-          <t>来源加法分按比例转移给目标</t>
+          <t>目标乘区*X(叠count次)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="H54" s="0" t="inlineStr">
         <is>
-          <t>ExtraSettlement</t>
+          <t>TransferScore</t>
         </is>
       </c>
       <c r="J54" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K54" s="0" t="inlineStr">
         <is>
-          <t>目标额外结算X次</t>
+          <t>来源加法分按比例转移给目标</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="H55" s="0" t="inlineStr">
         <is>
-          <t>TransferSkills</t>
+          <t>ExtraSettlement</t>
         </is>
       </c>
       <c r="J55" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K55" s="0" t="inlineStr">
         <is>
-          <t>来源技能传递给目标</t>
+          <t>目标额外结算X次</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="H56" s="0" t="inlineStr">
         <is>
-          <t>AddLayer</t>
+          <t>TransferSkills</t>
         </is>
       </c>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K56" s="0" t="inlineStr">
         <is>
-          <t>层数+X(mult时*X)</t>
+          <t>来源技能传递给目标</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="H57" s="0" t="inlineStr">
         <is>
-          <t>ConsumeLayer</t>
+          <t>AddLayer</t>
         </is>
       </c>
       <c r="J57" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K57" s="0" t="inlineStr">
         <is>
-          <t>层数-X</t>
+          <t>层数+X(mult时*X)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="H58" s="0" t="inlineStr">
         <is>
-          <t>GrantGold</t>
+          <t>ConsumeLayer</t>
         </is>
       </c>
       <c r="J58" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K58" s="0" t="inlineStr">
         <is>
-          <t>获得X*count金币</t>
+          <t>层数-X</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="H59" s="0" t="inlineStr">
         <is>
-          <t>AddMultFlat</t>
+          <t>GrantGold</t>
         </is>
       </c>
       <c r="J59" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K59" s="0" t="inlineStr">
         <is>
-          <t>目标乘区+X*count(加法叠加到倍率)</t>
+          <t>获得X*count金币</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="H60" s="0" t="inlineStr">
         <is>
-          <t>PermanentAddFlat</t>
+          <t>AddMultFlat</t>
         </is>
       </c>
       <c r="J60" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K60" s="0" t="inlineStr">
         <is>
-          <t>目标永久加法+X(跨结算持久)</t>
+          <t>目标乘区+X*count(加法叠加到倍率)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="H61" s="0" t="inlineStr">
         <is>
-          <t>PermanentAddMult</t>
+          <t>PermanentAddFlat</t>
         </is>
       </c>
       <c r="J61" s="0" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K61" s="0" t="inlineStr">
         <is>
-          <t>目标永久乘区*X(跨结算持久)</t>
+          <t>目标永久加法+X(跨结算持久)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="H62" s="0" t="inlineStr">
         <is>
-          <t>AddCountAs</t>
+          <t>PermanentAddMult</t>
         </is>
       </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K62" s="0" t="inlineStr">
         <is>
-          <t>目标"视为食物数"+X*count</t>
+          <t>目标永久乘区*X(跨结算持久)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="H63" s="0" t="inlineStr">
         <is>
-          <t>CopySkill</t>
+          <t>AddCountAs</t>
         </is>
       </c>
       <c r="J63" s="0" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K63" s="0" t="inlineStr">
         <is>
-          <t>从来源作用域随机复制actionCount个技能给目标</t>
+          <t>目标"视为食物数"+X*count</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="H64" s="0" t="inlineStr">
         <is>
+          <t>CopySkill</t>
+        </is>
+      </c>
+      <c r="J64" s="0" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K64" s="0" t="inlineStr">
+        <is>
+          <t>从来源作用域随机复制actionCount个技能给目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="H65" s="0" t="inlineStr">
+        <is>
           <t>TempCopyDish</t>
         </is>
       </c>
-      <c r="J64" s="0" t="inlineStr">
+      <c r="J65" s="0" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K64" s="0" t="inlineStr">
+      <c r="K65" s="0" t="inlineStr">
         <is>
           <t>临时复制目标菜到空格(本次品鉴)</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="E65" s="0" t="n"/>
-      <c r="F65" s="0" t="n"/>
-      <c r="G65" s="0" t="n"/>
-      <c r="H65" s="0" t="inlineStr">
+    <row r="66">
+      <c r="E66" s="0" t="n"/>
+      <c r="F66" s="0" t="n"/>
+      <c r="G66" s="0" t="n"/>
+      <c r="H66" s="0" t="inlineStr">
         <is>
           <t>TriggerSweetTransfer</t>
         </is>
       </c>
-      <c r="J65" s="0" t="inlineStr">
+      <c r="J66" s="0" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K65" s="0" t="inlineStr">
+      <c r="K66" s="0" t="inlineStr">
         <is>
           <t>触发作用域内食物各执行一次自身甜蜜传递</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="0" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>SkillTrigger</t>
         </is>
       </c>
-      <c r="C66" s="0" t="inlineStr">
+      <c r="C67" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D66" s="0" t="inlineStr">
+      <c r="D67" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F66" s="0" t="inlineStr">
+      <c r="F67" s="0" t="inlineStr">
         <is>
           <t>技能触发时机</t>
         </is>
       </c>
-      <c r="H66" s="0" t="inlineStr">
+      <c r="H67" s="0" t="inlineStr">
         <is>
           <t>OnSettle</t>
         </is>
       </c>
-      <c r="J66" s="0" t="inlineStr">
+      <c r="J67" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K66" s="0" t="inlineStr">
+      <c r="K67" s="0" t="inlineStr">
         <is>
           <t>结算时</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="H67" s="0" t="inlineStr">
+    <row r="68">
+      <c r="H68" s="0" t="inlineStr">
         <is>
           <t>OnServe</t>
         </is>
       </c>
-      <c r="J67" s="0" t="inlineStr">
+      <c r="J68" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K67" s="0" t="inlineStr">
+      <c r="K68" s="0" t="inlineStr">
         <is>
           <t>上菜时</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1606,820 +1606,837 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="0" t="inlineStr">
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>SkillCount</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>本菜技能数(包括甜蜜传递过来的技能)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>SkillScope</t>
         </is>
       </c>
-      <c r="C28" s="0" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F28" s="0" t="inlineStr">
+      <c r="F29" s="0" t="inlineStr">
         <is>
           <t>技能作用域</t>
         </is>
       </c>
-      <c r="H28" s="0" t="inlineStr">
+      <c r="H29" s="0" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="J28" s="0" t="inlineStr">
+      <c r="J29" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K28" s="0" t="inlineStr">
+      <c r="K29" s="0" t="inlineStr">
         <is>
           <t>本菜自身</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="H29" s="0" t="inlineStr">
-        <is>
-          <t>Adjacent</t>
-        </is>
-      </c>
-      <c r="J29" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" s="0" t="inlineStr">
-        <is>
-          <t>相邻菜</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>Row</t>
+          <t>Adjacent</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K30" s="0" t="inlineStr">
         <is>
-          <t>本行</t>
+          <t>相邻菜</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>Column</t>
+          <t>Row</t>
         </is>
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K31" s="0" t="inlineStr">
         <is>
-          <t>本列</t>
+          <t>本行</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Column</t>
         </is>
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t>全部菜</t>
+          <t>本列</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t>Empty</t>
+          <t>All</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t>空格</t>
+          <t>全部菜</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="H34" s="0" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Empty</t>
         </is>
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t>边缘</t>
+          <t>空格</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t>上菜顺序在前</t>
+          <t>边缘</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>Before</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t>上菜顺序在后</t>
+          <t>上菜顺序在前</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>Recipe</t>
+          <t>After</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t>菜谱</t>
+          <t>上菜顺序在后</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Recipe</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t>指定分类(condParam/actionParam)的菜</t>
+          <t>菜谱</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="H39" s="0" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K39" s="0" t="inlineStr">
+        <is>
+          <t>指定分类(condParam/actionParam)的菜</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="H40" s="0" t="inlineStr">
+        <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="J39" s="0" t="inlineStr">
+      <c r="J40" s="0" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K39" s="0" t="inlineStr">
+      <c r="K40" s="0" t="inlineStr">
         <is>
           <t>周围菜(共边相邻+对角相邻)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="0" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>CompareOp</t>
         </is>
       </c>
-      <c r="C40" s="0" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D40" s="0" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F40" s="0" t="inlineStr">
+      <c r="F41" s="0" t="inlineStr">
         <is>
           <t>比较符</t>
         </is>
       </c>
-      <c r="H40" s="0" t="inlineStr">
+      <c r="H41" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J40" s="0" t="inlineStr">
+      <c r="J41" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K40" s="0" t="inlineStr">
+      <c r="K41" s="0" t="inlineStr">
         <is>
           <t>不比较</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="H41" s="0" t="inlineStr">
-        <is>
-          <t>Gte</t>
-        </is>
-      </c>
-      <c r="J41" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" s="0" t="inlineStr">
-        <is>
-          <t>大于等于</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t>Lte</t>
+          <t>Gte</t>
         </is>
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K42" s="0" t="inlineStr">
         <is>
-          <t>小于等于</t>
+          <t>大于等于</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>Eq</t>
+          <t>Lte</t>
         </is>
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K43" s="0" t="inlineStr">
         <is>
-          <t>等于</t>
+          <t>小于等于</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t>Gt</t>
+          <t>Eq</t>
         </is>
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K44" s="0" t="inlineStr">
         <is>
-          <t>大于</t>
+          <t>等于</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="H45" s="0" t="inlineStr">
         <is>
+          <t>Gt</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K45" s="0" t="inlineStr">
+        <is>
+          <t>大于</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="H46" s="0" t="inlineStr">
+        <is>
           <t>Lt</t>
         </is>
       </c>
-      <c r="J45" s="0" t="inlineStr">
+      <c r="J46" s="0" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K45" s="0" t="inlineStr">
+      <c r="K46" s="0" t="inlineStr">
         <is>
           <t>小于</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="0" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>CountMode</t>
         </is>
       </c>
-      <c r="C46" s="0" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D46" s="0" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F46" s="0" t="inlineStr">
+      <c r="F47" s="0" t="inlineStr">
         <is>
           <t>计数模式</t>
         </is>
       </c>
-      <c r="H46" s="0" t="inlineStr">
+      <c r="H47" s="0" t="inlineStr">
         <is>
           <t>Per</t>
         </is>
       </c>
-      <c r="J46" s="0" t="inlineStr">
+      <c r="J47" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K46" s="0" t="inlineStr">
+      <c r="K47" s="0" t="inlineStr">
         <is>
           <t>每有1个:count=raw</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="H47" s="0" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="J47" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" s="0" t="inlineStr">
-        <is>
-          <t>达到阈值:闸门</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="H48" s="0" t="inlineStr">
         <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" s="0" t="inlineStr">
+        <is>
+          <t>达到阈值:闸门</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="H49" s="0" t="inlineStr">
+        <is>
           <t>Gate</t>
         </is>
       </c>
-      <c r="J48" s="0" t="inlineStr">
+      <c r="J49" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K48" s="0" t="inlineStr">
+      <c r="K49" s="0" t="inlineStr">
         <is>
           <t>布尔条件:闸门</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="0" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>CountUnit</t>
         </is>
       </c>
-      <c r="C49" s="0" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D49" s="0" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F49" s="0" t="inlineStr">
+      <c r="F50" s="0" t="inlineStr">
         <is>
           <t>计数单位</t>
         </is>
       </c>
-      <c r="H49" s="0" t="inlineStr">
+      <c r="H50" s="0" t="inlineStr">
         <is>
           <t>Instances</t>
         </is>
       </c>
-      <c r="J49" s="0" t="inlineStr">
+      <c r="J50" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K49" s="0" t="inlineStr">
+      <c r="K50" s="0" t="inlineStr">
         <is>
           <t>按实例(个)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="H50" s="0" t="inlineStr">
+    <row r="51">
+      <c r="H51" s="0" t="inlineStr">
         <is>
           <t>Kinds</t>
         </is>
       </c>
-      <c r="J50" s="0" t="inlineStr">
+      <c r="J51" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K50" s="0" t="inlineStr">
+      <c r="K51" s="0" t="inlineStr">
         <is>
           <t>按BaseId去重(种)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="0" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>SkillActionType</t>
         </is>
       </c>
-      <c r="C51" s="0" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D51" s="0" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F51" s="0" t="inlineStr">
+      <c r="F52" s="0" t="inlineStr">
         <is>
           <t>技能行为类型</t>
         </is>
       </c>
-      <c r="H51" s="0" t="inlineStr">
+      <c r="H52" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J51" s="0" t="inlineStr">
+      <c r="J52" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K51" s="0" t="inlineStr">
+      <c r="K52" s="0" t="inlineStr">
         <is>
           <t>无行为</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="H52" s="0" t="inlineStr">
-        <is>
-          <t>AddFlat</t>
-        </is>
-      </c>
-      <c r="J52" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" s="0" t="inlineStr">
-        <is>
-          <t>目标加法区+X*count</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="H53" s="0" t="inlineStr">
         <is>
-          <t>AddMult</t>
+          <t>AddFlat</t>
         </is>
       </c>
       <c r="J53" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K53" s="0" t="inlineStr">
         <is>
-          <t>目标乘区*X(叠count次)</t>
+          <t>目标加法区+X*count</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="H54" s="0" t="inlineStr">
         <is>
-          <t>TransferScore</t>
+          <t>AddMult</t>
         </is>
       </c>
       <c r="J54" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K54" s="0" t="inlineStr">
         <is>
-          <t>来源加法分按比例转移给目标</t>
+          <t>目标乘区*X(叠count次)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="H55" s="0" t="inlineStr">
         <is>
-          <t>ExtraSettlement</t>
+          <t>TransferScore</t>
         </is>
       </c>
       <c r="J55" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K55" s="0" t="inlineStr">
         <is>
-          <t>目标额外结算X次</t>
+          <t>来源加法分按比例转移给目标</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="H56" s="0" t="inlineStr">
         <is>
-          <t>TransferSkills</t>
+          <t>ExtraSettlement</t>
         </is>
       </c>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K56" s="0" t="inlineStr">
         <is>
-          <t>来源技能传递给目标</t>
+          <t>目标额外结算X次</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="H57" s="0" t="inlineStr">
         <is>
-          <t>AddLayer</t>
+          <t>TransferSkills</t>
         </is>
       </c>
       <c r="J57" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K57" s="0" t="inlineStr">
         <is>
-          <t>层数+X(mult时*X)</t>
+          <t>来源技能传递给目标</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="H58" s="0" t="inlineStr">
         <is>
-          <t>ConsumeLayer</t>
+          <t>AddLayer</t>
         </is>
       </c>
       <c r="J58" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K58" s="0" t="inlineStr">
         <is>
-          <t>层数-X</t>
+          <t>层数+X(mult时*X)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="H59" s="0" t="inlineStr">
         <is>
-          <t>GrantGold</t>
+          <t>ConsumeLayer</t>
         </is>
       </c>
       <c r="J59" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K59" s="0" t="inlineStr">
         <is>
-          <t>获得X*count金币</t>
+          <t>层数-X</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="H60" s="0" t="inlineStr">
         <is>
-          <t>AddMultFlat</t>
+          <t>GrantGold</t>
         </is>
       </c>
       <c r="J60" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K60" s="0" t="inlineStr">
         <is>
-          <t>目标乘区+X*count(加法叠加到倍率)</t>
+          <t>获得X*count金币</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="H61" s="0" t="inlineStr">
         <is>
-          <t>PermanentAddFlat</t>
+          <t>AddMultFlat</t>
         </is>
       </c>
       <c r="J61" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K61" s="0" t="inlineStr">
         <is>
-          <t>目标永久加法+X(跨结算持久)</t>
+          <t>目标乘区+X*count(加法叠加到倍率)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="H62" s="0" t="inlineStr">
         <is>
-          <t>PermanentAddMult</t>
+          <t>PermanentAddFlat</t>
         </is>
       </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K62" s="0" t="inlineStr">
         <is>
-          <t>目标永久乘区*X(跨结算持久)</t>
+          <t>目标永久加法+X(跨结算持久)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="H63" s="0" t="inlineStr">
         <is>
-          <t>AddCountAs</t>
+          <t>PermanentAddMult</t>
         </is>
       </c>
       <c r="J63" s="0" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K63" s="0" t="inlineStr">
         <is>
-          <t>目标"视为食物数"+X*count</t>
+          <t>目标永久乘区*X(跨结算持久)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="H64" s="0" t="inlineStr">
         <is>
-          <t>CopySkill</t>
+          <t>AddCountAs</t>
         </is>
       </c>
       <c r="J64" s="0" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K64" s="0" t="inlineStr">
         <is>
-          <t>从来源作用域随机复制actionCount个技能给目标</t>
+          <t>目标"视为食物数"+X*count</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="H65" s="0" t="inlineStr">
         <is>
+          <t>CopySkill</t>
+        </is>
+      </c>
+      <c r="J65" s="0" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K65" s="0" t="inlineStr">
+        <is>
+          <t>从来源作用域随机复制actionCount个技能给目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="H66" s="0" t="inlineStr">
+        <is>
           <t>TempCopyDish</t>
         </is>
       </c>
-      <c r="J65" s="0" t="inlineStr">
+      <c r="J66" s="0" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K65" s="0" t="inlineStr">
+      <c r="K66" s="0" t="inlineStr">
         <is>
           <t>临时复制目标菜到空格(本次品鉴)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="E66" s="0" t="n"/>
-      <c r="F66" s="0" t="n"/>
-      <c r="G66" s="0" t="n"/>
-      <c r="H66" s="0" t="inlineStr">
+    <row r="67">
+      <c r="E67" s="0" t="n"/>
+      <c r="F67" s="0" t="n"/>
+      <c r="G67" s="0" t="n"/>
+      <c r="H67" s="0" t="inlineStr">
         <is>
           <t>TriggerSweetTransfer</t>
         </is>
       </c>
-      <c r="J66" s="0" t="inlineStr">
+      <c r="J67" s="0" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K66" s="0" t="inlineStr">
+      <c r="K67" s="0" t="inlineStr">
         <is>
           <t>触发作用域内食物各执行一次自身甜蜜传递</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="0" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>SkillTrigger</t>
         </is>
       </c>
-      <c r="C67" s="0" t="inlineStr">
+      <c r="C68" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D67" s="0" t="inlineStr">
+      <c r="D68" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F67" s="0" t="inlineStr">
+      <c r="F68" s="0" t="inlineStr">
         <is>
           <t>技能触发时机</t>
         </is>
       </c>
-      <c r="H67" s="0" t="inlineStr">
+      <c r="H68" s="0" t="inlineStr">
         <is>
           <t>OnSettle</t>
         </is>
       </c>
-      <c r="J67" s="0" t="inlineStr">
+      <c r="J68" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K67" s="0" t="inlineStr">
+      <c r="K68" s="0" t="inlineStr">
         <is>
           <t>结算时</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="H68" s="0" t="inlineStr">
+    <row r="69">
+      <c r="H69" s="0" t="inlineStr">
         <is>
           <t>OnServe</t>
         </is>
       </c>
-      <c r="J68" s="0" t="inlineStr">
+      <c r="J69" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K68" s="0" t="inlineStr">
+      <c r="K69" s="0" t="inlineStr">
         <is>
           <t>上菜时</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1297,891 +1297,867 @@
       <c r="L10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>SkillConditionType</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D11" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t>技能前提类型</t>
-        </is>
-      </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J11" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>GrantGold</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>7</v>
       </c>
       <c r="K11" s="0" t="inlineStr">
         <is>
-          <t>无前提，恒触发一次</t>
+          <t>结算时获得金币(锈)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>PositionFilled</t>
-        </is>
-      </c>
-      <c r="J12" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>SettlementLayer</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>8</v>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t>作用域存在格是否全被占满(闸门)</t>
+          <t>结算优先级层级增量(甜+1/苦-1)，不产生分数效果</t>
         </is>
       </c>
     </row>
     <row r="13">
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>SkillConditionType</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>技能前提类型</t>
+        </is>
+      </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>EmptyCell</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t>作用域内空格数</t>
+          <t>无前提，恒触发一次</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>PositionFilled</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t>本菜是否处于棋盘边缘(闸门)</t>
+          <t>作用域存在格是否全被占满(闸门)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>DishCount</t>
+          <t>EmptyCell</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t>作用域内菜数</t>
+          <t>作用域内空格数</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>DishSize</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t>作用域内占格数比较阈值的菜数</t>
+          <t>本菜是否处于棋盘边缘(闸门)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>ServeOrder</t>
+          <t>DishCount</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t>上菜顺序在前/后的菜数</t>
+          <t>作用域内菜数</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>SameDish</t>
+          <t>DishSize</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t>作用域内同BaseId的菜数</t>
+          <t>作用域内占格数比较阈值的菜数</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t>SameKindInRun</t>
+          <t>ServeOrder</t>
         </is>
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K19" s="0" t="inlineStr">
         <is>
-          <t>本局已结算过本种的次数</t>
+          <t>上菜顺序在前/后的菜数</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t>SameKindInMeal</t>
+          <t>SameDish</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t>本次品鉴本种数量/已结算次数</t>
+          <t>作用域内同BaseId的菜数</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t>TagCount</t>
+          <t>SameKindInRun</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t>本菜标签数</t>
+          <t>本局已结算过本种的次数</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>ShapeMatch</t>
+          <t>SameKindInMeal</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t>作用域内形状匹配condParam的菜数</t>
+          <t>本次品鉴本种数量/已结算次数</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t>RecipeCount</t>
+          <t>TagCount</t>
         </is>
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t>菜谱内菜数比较阈值(闸门)</t>
+          <t>本菜标签数</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t>LayerCount</t>
+          <t>ShapeMatch</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t>本菜当前层数</t>
+          <t>作用域内形状匹配condParam的菜数</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="H25" s="0" t="inlineStr">
         <is>
-          <t>OccupiedCell</t>
+          <t>RecipeCount</t>
         </is>
       </c>
       <c r="J25" s="0" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K25" s="0" t="inlineStr">
         <is>
-          <t>本菜占用格数</t>
+          <t>菜谱内菜数比较阈值(闸门)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t>CategoryCount</t>
+          <t>LayerCount</t>
         </is>
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t>作用域内指定分类(condParam)的菜数</t>
+          <t>本菜当前层数</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>SkillTypeCount</t>
+          <t>OccupiedCell</t>
         </is>
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K27" s="0" t="inlineStr">
         <is>
-          <t>作用域内带某行为类技能(condParam)的菜数</t>
+          <t>本菜占用格数</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>SkillCount</t>
+          <t>CategoryCount</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K28" s="0" t="inlineStr">
         <is>
-          <t>本菜技能数(包括甜蜜传递过来的技能)</t>
+          <t>作用域内指定分类(condParam)的菜数</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="0" t="inlineStr">
-        <is>
-          <t>SkillScope</t>
-        </is>
-      </c>
-      <c r="C29" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D29" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F29" s="0" t="inlineStr">
-        <is>
-          <t>技能作用域</t>
-        </is>
-      </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>SkillTypeCount</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t>本菜自身</t>
+          <t>作用域内带某行为类技能(condParam)的菜数</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>Adjacent</t>
+          <t>SkillCount</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K30" s="0" t="inlineStr">
         <is>
-          <t>相邻菜</t>
+          <t>本菜技能数(包括甜蜜传递过来的技能)</t>
         </is>
       </c>
     </row>
     <row r="31">
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>SkillScope</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="inlineStr">
+        <is>
+          <t>技能作用域</t>
+        </is>
+      </c>
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>Row</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K31" s="0" t="inlineStr">
         <is>
-          <t>同行</t>
+          <t>本菜自身</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>Column</t>
+          <t>Adjacent</t>
         </is>
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t>同列</t>
+          <t>相邻菜</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Row</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t>全部菜</t>
+          <t>同行</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="H34" s="0" t="inlineStr">
         <is>
-          <t>Empty</t>
+          <t>Column</t>
         </is>
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t>空格</t>
+          <t>同列</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>All</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t>边缘</t>
+          <t>全部菜</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Empty</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t>上菜顺序在前</t>
+          <t>空格</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t>上菜顺序在后</t>
+          <t>边缘</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>Recipe</t>
+          <t>Before</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t>菜谱</t>
+          <t>上菜顺序在前</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>After</t>
         </is>
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K39" s="0" t="inlineStr">
         <is>
-          <t>指定分类(condParam/actionParam)的菜</t>
+          <t>上菜顺序在后</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Recipe</t>
         </is>
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K40" s="0" t="inlineStr">
         <is>
-          <t>周围菜(共边相邻+对角相邻)</t>
+          <t>菜谱</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>RoundAndSelf</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K41" s="0" t="inlineStr">
         <is>
-          <t>周围及自身(周围菜+本菜自身)</t>
+          <t>指定分类(condParam/actionParam)的菜</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t>RowAndSelf</t>
+          <t>Round</t>
         </is>
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K42" s="0" t="inlineStr">
         <is>
-          <t>本行(同行+自身)</t>
+          <t>周围菜(共边相邻+对角相邻)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>ColumnAndSelf</t>
+          <t>RoundAndSelf</t>
         </is>
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K43" s="0" t="inlineStr">
         <is>
-          <t>本列（同列+自身）</t>
+          <t>周围及自身(周围菜+本菜自身)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>RowAndSelf</t>
         </is>
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K44" s="0" t="inlineStr">
         <is>
-          <t>其他菜（全部菜-本菜自身）</t>
+          <t>本行(同行+自身)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="H45" s="0" t="inlineStr">
         <is>
-          <t>CakeBuff</t>
+          <t>ColumnAndSelf</t>
         </is>
       </c>
       <c r="J45" s="0" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K45" s="0" t="inlineStr">
         <is>
-          <t>全局欢乐蛋糕层数效果</t>
+          <t>本列（同列+自身）</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="0" t="inlineStr">
-        <is>
-          <t>CompareOp</t>
-        </is>
-      </c>
-      <c r="C46" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D46" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F46" s="0" t="inlineStr">
-        <is>
-          <t>比较符</t>
-        </is>
-      </c>
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="J46" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K46" s="0" t="inlineStr">
         <is>
-          <t>不比较</t>
+          <t>其他菜（全部菜-本菜自身）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="H47" s="0" t="inlineStr">
         <is>
-          <t>Gte</t>
+          <t>CakeBuff</t>
         </is>
       </c>
       <c r="J47" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K47" s="0" t="inlineStr">
         <is>
-          <t>大于等于</t>
+          <t>全局欢乐蛋糕层数效果</t>
         </is>
       </c>
     </row>
     <row r="48">
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>CompareOp</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F48" s="0" t="inlineStr">
+        <is>
+          <t>比较符</t>
+        </is>
+      </c>
       <c r="H48" s="0" t="inlineStr">
         <is>
-          <t>Lte</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J48" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K48" s="0" t="inlineStr">
         <is>
-          <t>小于等于</t>
+          <t>不比较</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="H49" s="0" t="inlineStr">
         <is>
-          <t>Eq</t>
+          <t>Gte</t>
         </is>
       </c>
       <c r="J49" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K49" s="0" t="inlineStr">
         <is>
-          <t>等于</t>
+          <t>大于等于</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="H50" s="0" t="inlineStr">
         <is>
-          <t>Gt</t>
+          <t>Lte</t>
         </is>
       </c>
       <c r="J50" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K50" s="0" t="inlineStr">
         <is>
-          <t>大于</t>
+          <t>小于等于</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="H51" s="0" t="inlineStr">
         <is>
-          <t>Lt</t>
+          <t>Eq</t>
         </is>
       </c>
       <c r="J51" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K51" s="0" t="inlineStr">
         <is>
-          <t>小于</t>
+          <t>等于</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="0" t="inlineStr">
-        <is>
-          <t>CountMode</t>
-        </is>
-      </c>
-      <c r="C52" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D52" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F52" s="0" t="inlineStr">
-        <is>
-          <t>计数模式</t>
-        </is>
-      </c>
       <c r="H52" s="0" t="inlineStr">
         <is>
-          <t>Per</t>
+          <t>Gt</t>
         </is>
       </c>
       <c r="J52" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K52" s="0" t="inlineStr">
         <is>
-          <t>每有1个:count=raw</t>
+          <t>大于</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="H53" s="0" t="inlineStr">
         <is>
+          <t>Lt</t>
+        </is>
+      </c>
+      <c r="J53" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K53" s="0" t="inlineStr">
+        <is>
+          <t>小于</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>CountMode</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F54" s="0" t="inlineStr">
+        <is>
+          <t>计数模式</t>
+        </is>
+      </c>
+      <c r="H54" s="0" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J54" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K54" s="0" t="inlineStr">
+        <is>
+          <t>每有1个:count=raw</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="H55" s="0" t="inlineStr">
+        <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="J53" s="0" t="inlineStr">
+      <c r="J55" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K53" s="0" t="inlineStr">
+      <c r="K55" s="0" t="inlineStr">
         <is>
           <t>达到阈值:闸门</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="H54" s="0" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="J54" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" s="0" t="inlineStr">
-        <is>
-          <t>布尔条件:闸门</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="0" t="inlineStr">
-        <is>
-          <t>CountUnit</t>
-        </is>
-      </c>
-      <c r="C55" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D55" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F55" s="0" t="inlineStr">
-        <is>
-          <t>计数单位</t>
-        </is>
-      </c>
-      <c r="H55" s="0" t="inlineStr">
-        <is>
-          <t>Instances</t>
-        </is>
-      </c>
-      <c r="J55" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K55" s="0" t="inlineStr">
-        <is>
-          <t>按实例(个)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="H56" s="0" t="inlineStr">
         <is>
-          <t>Kinds</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K56" s="0" t="inlineStr">
         <is>
-          <t>按BaseId去重(种)</t>
+          <t>布尔条件:闸门</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>SkillActionType</t>
+          <t>CountUnit</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -2196,12 +2172,12 @@
       </c>
       <c r="F57" s="0" t="inlineStr">
         <is>
-          <t>技能行为类型</t>
+          <t>计数单位</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Instances</t>
         </is>
       </c>
       <c r="J57" s="0" t="inlineStr">
@@ -2211,14 +2187,14 @@
       </c>
       <c r="K57" s="0" t="inlineStr">
         <is>
-          <t>无行为</t>
+          <t>按实例(个)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="H58" s="0" t="inlineStr">
         <is>
-          <t>AddFlat</t>
+          <t>Kinds</t>
         </is>
       </c>
       <c r="J58" s="0" t="inlineStr">
@@ -2228,302 +2204,496 @@
       </c>
       <c r="K58" s="0" t="inlineStr">
         <is>
-          <t>目标加法区+X*count</t>
+          <t>按BaseId去重(种)</t>
         </is>
       </c>
     </row>
     <row r="59">
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>SkillActionType</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F59" s="0" t="inlineStr">
+        <is>
+          <t>技能行为类型</t>
+        </is>
+      </c>
       <c r="H59" s="0" t="inlineStr">
         <is>
-          <t>AddMult</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J59" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K59" s="0" t="inlineStr">
         <is>
-          <t>目标乘区*X(叠count次)</t>
+          <t>无行为</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="H60" s="0" t="inlineStr">
         <is>
-          <t>TransferScore</t>
+          <t>AddFlat</t>
         </is>
       </c>
       <c r="J60" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K60" s="0" t="inlineStr">
         <is>
-          <t>来源加法分按比例转移给目标</t>
+          <t>目标加法区+X*count</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="H61" s="0" t="inlineStr">
         <is>
-          <t>ExtraSettlement</t>
+          <t>AddMult</t>
         </is>
       </c>
       <c r="J61" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K61" s="0" t="inlineStr">
         <is>
-          <t>目标额外结算X次</t>
+          <t>目标乘区*X(叠count次)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="H62" s="0" t="inlineStr">
         <is>
-          <t>TransferSkills</t>
+          <t>TransferScore</t>
         </is>
       </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K62" s="0" t="inlineStr">
         <is>
-          <t>来源技能传递给目标</t>
+          <t>来源加法分按比例转移给目标</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="H63" s="0" t="inlineStr">
         <is>
-          <t>AddLayer</t>
+          <t>ExtraSettlement</t>
         </is>
       </c>
       <c r="J63" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K63" s="0" t="inlineStr">
         <is>
-          <t>层数+X(mult时*X)</t>
+          <t>目标额外结算X次</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="H64" s="0" t="inlineStr">
         <is>
-          <t>ConsumeLayer</t>
+          <t>TransferSkills</t>
         </is>
       </c>
       <c r="J64" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K64" s="0" t="inlineStr">
         <is>
-          <t>层数-X</t>
+          <t>来源技能传递给目标</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="H65" s="0" t="inlineStr">
         <is>
-          <t>GrantGold</t>
+          <t>AddLayer</t>
         </is>
       </c>
       <c r="J65" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K65" s="0" t="inlineStr">
         <is>
-          <t>获得X*count金币</t>
+          <t>层数+X(mult时*X)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="H66" s="0" t="inlineStr">
         <is>
-          <t>AddMultFlat</t>
+          <t>ConsumeLayer</t>
         </is>
       </c>
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K66" s="0" t="inlineStr">
         <is>
-          <t>目标乘区+X*count(加法叠加到倍率)</t>
+          <t>层数-X</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="H67" s="0" t="inlineStr">
         <is>
-          <t>PermanentAddFlat</t>
+          <t>GrantGold</t>
         </is>
       </c>
       <c r="J67" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K67" s="0" t="inlineStr">
         <is>
-          <t>目标永久加法+X(跨结算持久)</t>
+          <t>获得X*count金币</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="H68" s="0" t="inlineStr">
         <is>
-          <t>PermanentAddMult</t>
+          <t>AddMultFlat</t>
         </is>
       </c>
       <c r="J68" s="0" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K68" s="0" t="inlineStr">
         <is>
-          <t>目标永久乘区*X(跨结算持久)</t>
+          <t>目标乘区+X*count(加法叠加到倍率)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="H69" s="0" t="inlineStr">
         <is>
-          <t>AddCountAs</t>
+          <t>PermanentAddFlat</t>
         </is>
       </c>
       <c r="J69" s="0" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K69" s="0" t="inlineStr">
         <is>
-          <t>目标"视为食物数"+X*count</t>
+          <t>目标永久加法+X(跨结算持久)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="H70" s="0" t="inlineStr">
         <is>
-          <t>CopySkill</t>
+          <t>PermanentAddMult</t>
         </is>
       </c>
       <c r="J70" s="0" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K70" s="0" t="inlineStr">
         <is>
-          <t>从来源作用域随机复制actionCount个技能给目标</t>
+          <t>目标永久乘区*X(跨结算持久)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="H71" s="0" t="inlineStr">
         <is>
+          <t>AddCountAs</t>
+        </is>
+      </c>
+      <c r="J71" s="0" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K71" s="0" t="inlineStr">
+        <is>
+          <t>目标"视为食物数"+X*count</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="H72" s="0" t="inlineStr">
+        <is>
+          <t>CopySkill</t>
+        </is>
+      </c>
+      <c r="J72" s="0" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K72" s="0" t="inlineStr">
+        <is>
+          <t>从来源作用域随机复制actionCount个技能给目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="H73" s="0" t="inlineStr">
+        <is>
           <t>TempCopyDish</t>
         </is>
       </c>
-      <c r="J71" s="0" t="inlineStr">
+      <c r="J73" s="0" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K71" s="0" t="inlineStr">
+      <c r="K73" s="0" t="inlineStr">
         <is>
           <t>临时复制目标菜到空格(本次品鉴)</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="E72" s="0" t="n"/>
-      <c r="F72" s="0" t="n"/>
-      <c r="G72" s="0" t="n"/>
-      <c r="H72" s="0" t="inlineStr">
+    <row r="74">
+      <c r="E74" s="0" t="n"/>
+      <c r="F74" s="0" t="n"/>
+      <c r="G74" s="0" t="n"/>
+      <c r="H74" s="0" t="inlineStr">
         <is>
           <t>TriggerSweetTransfer</t>
         </is>
       </c>
-      <c r="J72" s="0" t="inlineStr">
+      <c r="J74" s="0" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K72" s="0" t="inlineStr">
+      <c r="K74" s="0" t="inlineStr">
         <is>
           <t>触发作用域内食物各执行一次自身甜蜜传递</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="0" t="inlineStr">
+    <row r="75">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>SkillTrigger</t>
         </is>
       </c>
-      <c r="C73" s="0" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D73" s="0" t="inlineStr">
+      <c r="D75" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F73" s="0" t="inlineStr">
+      <c r="F75" s="0" t="inlineStr">
         <is>
           <t>技能触发时机</t>
         </is>
       </c>
-      <c r="H73" s="0" t="inlineStr">
+      <c r="H75" s="0" t="inlineStr">
         <is>
           <t>OnSettle</t>
         </is>
       </c>
-      <c r="J73" s="0" t="inlineStr">
+      <c r="J75" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K73" s="0" t="inlineStr">
+      <c r="K75" s="0" t="inlineStr">
         <is>
           <t>结算时</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="H74" s="0" t="inlineStr">
+    <row r="76">
+      <c r="H76" s="0" t="inlineStr">
         <is>
           <t>OnServe</t>
         </is>
       </c>
-      <c r="J74" s="0" t="inlineStr">
+      <c r="J76" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K74" s="0" t="inlineStr">
+      <c r="K76" s="0" t="inlineStr">
         <is>
           <t>上菜时</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MaterialEffectType</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>餐桌材质效果类型</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>分数+值(临时,樱桃木)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>PermanentAddFlat</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>2</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>分数永久+值(胡桃木)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>AddMultFlat</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>3</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>倍率+值(临时,大理石)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>AddMult</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>倍率×值(黑曜石)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>AddMultFlatPerCell</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>5</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>每占1格本材质倍率+值(翡翠)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>GrantGoldIfCellCount</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>6</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>占&gt;=阈值格获得金币(金)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>GrantItemRollIfCellCount</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>7</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>占&gt;=阈值格1/3获得主动道具(银)</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_tag.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1327,837 +1327,811 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="0" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Rotate</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>麻：逆时针旋转 value×90 度，不产生分数效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SourRecipeMult</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>酸：未上菜时场上同菜谱食物倍率×value</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SaltyRecipeGold</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>咸：未上菜时场上每个同菜谱食物+value金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>SkillConditionType</t>
         </is>
       </c>
-      <c r="C13" s="0" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D13" s="0" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F13" s="0" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>技能前提类型</t>
         </is>
       </c>
-      <c r="H13" s="0" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J13" s="0" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="0" t="inlineStr">
+      <c r="K16" s="0" t="inlineStr">
         <is>
           <t>无前提，恒触发一次</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="H14" s="0" t="inlineStr">
-        <is>
-          <t>PositionFilled</t>
-        </is>
-      </c>
-      <c r="J14" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="0" t="inlineStr">
-        <is>
-          <t>作用域存在格是否全被占满(闸门)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="H15" s="0" t="inlineStr">
-        <is>
-          <t>EmptyCell</t>
-        </is>
-      </c>
-      <c r="J15" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" s="0" t="inlineStr">
-        <is>
-          <t>作用域内空格数</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="H16" s="0" t="inlineStr">
-        <is>
-          <t>Edge</t>
-        </is>
-      </c>
-      <c r="J16" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="0" t="inlineStr">
-        <is>
-          <t>本菜是否处于棋盘边缘(闸门)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>DishCount</t>
+          <t>PositionFilled</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t>作用域内菜数</t>
+          <t>作用域存在格是否全被占满(闸门)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>DishSize</t>
+          <t>EmptyCell</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t>作用域内占格数比较阈值的菜数</t>
+          <t>作用域内空格数</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t>ServeOrder</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K19" s="0" t="inlineStr">
         <is>
-          <t>上菜顺序在前/后的菜数</t>
+          <t>本菜是否处于棋盘边缘(闸门)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t>SameDish</t>
+          <t>DishCount</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t>作用域内同BaseId的菜数</t>
+          <t>作用域内菜数</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t>SameKindInRun</t>
+          <t>DishSize</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t>本局已结算过本种的次数</t>
+          <t>作用域内占格数比较阈值的菜数</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>SameKindInMeal</t>
+          <t>ServeOrder</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t>本次品鉴本种数量/已结算次数</t>
+          <t>上菜顺序在前/后的菜数</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t>TagCount</t>
+          <t>SameDish</t>
         </is>
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t>本菜标签数</t>
+          <t>作用域内同BaseId的菜数</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t>ShapeMatch</t>
+          <t>SameKindInRun</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t>作用域内形状匹配condParam的菜数</t>
+          <t>本局已结算过本种的次数</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="H25" s="0" t="inlineStr">
         <is>
-          <t>RecipeCount</t>
+          <t>SameKindInMeal</t>
         </is>
       </c>
       <c r="J25" s="0" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K25" s="0" t="inlineStr">
         <is>
-          <t>菜谱内菜数比较阈值(闸门)</t>
+          <t>本次品鉴本种数量/已结算次数</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t>LayerCount</t>
+          <t>TagCount</t>
         </is>
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t>本菜当前层数</t>
+          <t>本菜标签数</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>OccupiedCell</t>
+          <t>ShapeMatch</t>
         </is>
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K27" s="0" t="inlineStr">
         <is>
-          <t>本菜占用格数</t>
+          <t>作用域内形状匹配condParam的菜数</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>CategoryCount</t>
+          <t>RecipeCount</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K28" s="0" t="inlineStr">
         <is>
-          <t>作用域内指定分类(condParam)的菜数</t>
+          <t>菜谱内菜数比较阈值(闸门)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>SkillTypeCount</t>
+          <t>LayerCount</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t>作用域内带某行为类技能(condParam)的菜数</t>
+          <t>本菜当前层数</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>SkillCount</t>
+          <t>OccupiedCell</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K30" s="0" t="inlineStr">
         <is>
-          <t>本菜技能数(包括甜蜜传递过来的技能)</t>
+          <t>本菜占用格数</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="0" t="inlineStr">
-        <is>
-          <t>SkillScope</t>
-        </is>
-      </c>
-      <c r="C31" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F31" s="0" t="inlineStr">
-        <is>
-          <t>技能作用域</t>
-        </is>
-      </c>
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>CategoryCount</t>
         </is>
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K31" s="0" t="inlineStr">
         <is>
-          <t>本菜自身</t>
+          <t>作用域内指定分类(condParam)的菜数</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>Adjacent</t>
+          <t>SkillTypeCount</t>
         </is>
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t>相邻菜</t>
+          <t>作用域内带某行为类技能(condParam)的菜数</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t>Row</t>
+          <t>SkillCount</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t>同行</t>
+          <t>本菜技能数(包括甜蜜传递过来的技能)</t>
         </is>
       </c>
     </row>
     <row r="34">
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>SkillScope</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F34" s="0" t="inlineStr">
+        <is>
+          <t>技能作用域</t>
+        </is>
+      </c>
       <c r="H34" s="0" t="inlineStr">
         <is>
-          <t>Column</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t>同列</t>
+          <t>本菜自身</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Adjacent</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t>全部菜</t>
+          <t>相邻菜</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>Empty</t>
+          <t>Row</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t>空格</t>
+          <t>同行</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Column</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t>边缘</t>
+          <t>同列</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>All</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t>上菜顺序在前</t>
+          <t>全部菜</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>Empty</t>
         </is>
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K39" s="0" t="inlineStr">
         <is>
-          <t>上菜顺序在后</t>
+          <t>空格</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>Recipe</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K40" s="0" t="inlineStr">
         <is>
-          <t>菜谱</t>
+          <t>边缘</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Before</t>
         </is>
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K41" s="0" t="inlineStr">
         <is>
-          <t>指定分类(condParam/actionParam)的菜</t>
+          <t>上菜顺序在前</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>After</t>
         </is>
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K42" s="0" t="inlineStr">
         <is>
-          <t>周围菜(共边相邻+对角相邻)</t>
+          <t>上菜顺序在后</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>RoundAndSelf</t>
+          <t>Recipe</t>
         </is>
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K43" s="0" t="inlineStr">
         <is>
-          <t>周围及自身(周围菜+本菜自身)</t>
+          <t>菜谱</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t>RowAndSelf</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K44" s="0" t="inlineStr">
         <is>
-          <t>本行(同行+自身)</t>
+          <t>指定分类(condParam/actionParam)的菜</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="H45" s="0" t="inlineStr">
         <is>
-          <t>ColumnAndSelf</t>
+          <t>Round</t>
         </is>
       </c>
       <c r="J45" s="0" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K45" s="0" t="inlineStr">
         <is>
-          <t>本列（同列+自身）</t>
+          <t>周围菜(共边相邻+对角相邻)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>RoundAndSelf</t>
         </is>
       </c>
       <c r="J46" s="0" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K46" s="0" t="inlineStr">
         <is>
-          <t>其他菜（全部菜-本菜自身）</t>
+          <t>周围及自身(周围菜+本菜自身)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="H47" s="0" t="inlineStr">
         <is>
-          <t>CakeBuff</t>
+          <t>RowAndSelf</t>
         </is>
       </c>
       <c r="J47" s="0" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K47" s="0" t="inlineStr">
         <is>
-          <t>全局欢乐蛋糕层数效果</t>
+          <t>本行(同行+自身)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="0" t="inlineStr">
-        <is>
-          <t>CompareOp</t>
-        </is>
-      </c>
-      <c r="C48" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D48" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F48" s="0" t="inlineStr">
-        <is>
-          <t>比较符</t>
-        </is>
-      </c>
       <c r="H48" s="0" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ColumnAndSelf</t>
         </is>
       </c>
       <c r="J48" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K48" s="0" t="inlineStr">
         <is>
-          <t>不比较</t>
+          <t>本列（同列+自身）</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="H49" s="0" t="inlineStr">
         <is>
-          <t>Gte</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="J49" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K49" s="0" t="inlineStr">
         <is>
-          <t>大于等于</t>
+          <t>其他菜（全部菜-本菜自身）</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="H50" s="0" t="inlineStr">
         <is>
-          <t>Lte</t>
+          <t>CakeBuff</t>
         </is>
       </c>
       <c r="J50" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K50" s="0" t="inlineStr">
         <is>
-          <t>小于等于</t>
+          <t>全局欢乐蛋糕层数效果</t>
         </is>
       </c>
     </row>
     <row r="51">
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>CompareOp</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F51" s="0" t="inlineStr">
+        <is>
+          <t>比较符</t>
+        </is>
+      </c>
       <c r="H51" s="0" t="inlineStr">
         <is>
-          <t>Eq</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J51" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K51" s="0" t="inlineStr">
         <is>
-          <t>等于</t>
+          <t>不比较</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="H52" s="0" t="inlineStr">
         <is>
-          <t>Gt</t>
+          <t>Gte</t>
         </is>
       </c>
       <c r="J52" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" s="0" t="inlineStr">
         <is>
-          <t>大于</t>
+          <t>大于等于</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="H53" s="0" t="inlineStr">
         <is>
-          <t>Lt</t>
+          <t>Lte</t>
         </is>
       </c>
       <c r="J53" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K53" s="0" t="inlineStr">
         <is>
-          <t>小于</t>
+          <t>小于等于</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="0" t="inlineStr">
-        <is>
-          <t>CountMode</t>
-        </is>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D54" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F54" s="0" t="inlineStr">
-        <is>
-          <t>计数模式</t>
-        </is>
-      </c>
       <c r="H54" s="0" t="inlineStr">
         <is>
-          <t>Per</t>
+          <t>Eq</t>
         </is>
       </c>
       <c r="J54" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K54" s="0" t="inlineStr">
         <is>
-          <t>每有1个:count=raw</t>
+          <t>等于</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="H55" s="0" t="inlineStr">
         <is>
-          <t>Reach</t>
+          <t>Gt</t>
         </is>
       </c>
       <c r="J55" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K55" s="0" t="inlineStr">
         <is>
-          <t>达到阈值:闸门</t>
+          <t>大于</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="H56" s="0" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Lt</t>
         </is>
       </c>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K56" s="0" t="inlineStr">
         <is>
-          <t>布尔条件:闸门</t>
+          <t>小于</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>CountUnit</t>
+          <t>CountMode</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -2172,12 +2146,12 @@
       </c>
       <c r="F57" s="0" t="inlineStr">
         <is>
-          <t>计数单位</t>
+          <t>计数模式</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
         <is>
-          <t>Instances</t>
+          <t>Per</t>
         </is>
       </c>
       <c r="J57" s="0" t="inlineStr">
@@ -2187,14 +2161,14 @@
       </c>
       <c r="K57" s="0" t="inlineStr">
         <is>
-          <t>按实例(个)</t>
+          <t>每有1个:count=raw</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="H58" s="0" t="inlineStr">
         <is>
-          <t>Kinds</t>
+          <t>Reach</t>
         </is>
       </c>
       <c r="J58" s="0" t="inlineStr">
@@ -2204,494 +2178,565 @@
       </c>
       <c r="K58" s="0" t="inlineStr">
         <is>
-          <t>按BaseId去重(种)</t>
+          <t>达到阈值:闸门</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="0" t="inlineStr">
-        <is>
-          <t>SkillActionType</t>
-        </is>
-      </c>
-      <c r="C59" s="0" t="inlineStr">
+      <c r="H59" s="0" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="J59" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K59" s="0" t="inlineStr">
+        <is>
+          <t>布尔条件:闸门</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>CountUnit</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D59" s="0" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F59" s="0" t="inlineStr">
-        <is>
-          <t>技能行为类型</t>
-        </is>
-      </c>
-      <c r="H59" s="0" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J59" s="0" t="inlineStr">
+      <c r="F60" s="0" t="inlineStr">
+        <is>
+          <t>计数单位</t>
+        </is>
+      </c>
+      <c r="H60" s="0" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="J60" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K59" s="0" t="inlineStr">
-        <is>
-          <t>无行为</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="H60" s="0" t="inlineStr">
-        <is>
-          <t>AddFlat</t>
-        </is>
-      </c>
-      <c r="J60" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K60" s="0" t="inlineStr">
         <is>
-          <t>目标加法区+X*count</t>
+          <t>按实例(个)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="H61" s="0" t="inlineStr">
         <is>
-          <t>AddMult</t>
+          <t>Kinds</t>
         </is>
       </c>
       <c r="J61" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K61" s="0" t="inlineStr">
         <is>
-          <t>目标乘区*X(叠count次)</t>
+          <t>按BaseId去重(种)</t>
         </is>
       </c>
     </row>
     <row r="62">
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>SkillActionType</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D62" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F62" s="0" t="inlineStr">
+        <is>
+          <t>技能行为类型</t>
+        </is>
+      </c>
       <c r="H62" s="0" t="inlineStr">
         <is>
-          <t>TransferScore</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K62" s="0" t="inlineStr">
         <is>
-          <t>来源加法分按比例转移给目标</t>
+          <t>无行为</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="H63" s="0" t="inlineStr">
         <is>
-          <t>ExtraSettlement</t>
+          <t>AddFlat</t>
         </is>
       </c>
       <c r="J63" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K63" s="0" t="inlineStr">
         <is>
-          <t>目标额外结算X次</t>
+          <t>目标加法区+X*count</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="H64" s="0" t="inlineStr">
         <is>
-          <t>TransferSkills</t>
+          <t>AddMult</t>
         </is>
       </c>
       <c r="J64" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K64" s="0" t="inlineStr">
         <is>
-          <t>来源技能传递给目标</t>
+          <t>目标乘区*X(叠count次)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="H65" s="0" t="inlineStr">
         <is>
-          <t>AddLayer</t>
+          <t>TransferScore</t>
         </is>
       </c>
       <c r="J65" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K65" s="0" t="inlineStr">
         <is>
-          <t>层数+X(mult时*X)</t>
+          <t>来源加法分按比例转移给目标</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="H66" s="0" t="inlineStr">
         <is>
-          <t>ConsumeLayer</t>
+          <t>ExtraSettlement</t>
         </is>
       </c>
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K66" s="0" t="inlineStr">
         <is>
-          <t>层数-X</t>
+          <t>目标额外结算X次</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="H67" s="0" t="inlineStr">
         <is>
-          <t>GrantGold</t>
+          <t>TransferSkills</t>
         </is>
       </c>
       <c r="J67" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K67" s="0" t="inlineStr">
         <is>
-          <t>获得X*count金币</t>
+          <t>来源技能传递给目标</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="H68" s="0" t="inlineStr">
         <is>
-          <t>AddMultFlat</t>
+          <t>AddLayer</t>
         </is>
       </c>
       <c r="J68" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K68" s="0" t="inlineStr">
         <is>
-          <t>目标乘区+X*count(加法叠加到倍率)</t>
+          <t>层数+X(mult时*X)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="H69" s="0" t="inlineStr">
         <is>
-          <t>PermanentAddFlat</t>
+          <t>ConsumeLayer</t>
         </is>
       </c>
       <c r="J69" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K69" s="0" t="inlineStr">
         <is>
-          <t>目标永久加法+X(跨结算持久)</t>
+          <t>层数-X</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="H70" s="0" t="inlineStr">
         <is>
-          <t>PermanentAddMult</t>
+          <t>GrantGold</t>
         </is>
       </c>
       <c r="J70" s="0" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K70" s="0" t="inlineStr">
         <is>
-          <t>目标永久乘区*X(跨结算持久)</t>
+          <t>获得X*count金币</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="H71" s="0" t="inlineStr">
         <is>
-          <t>AddCountAs</t>
+          <t>AddMultFlat</t>
         </is>
       </c>
       <c r="J71" s="0" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K71" s="0" t="inlineStr">
         <is>
-          <t>目标"视为食物数"+X*count</t>
+          <t>目标乘区+X*count(加法叠加到倍率)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="H72" s="0" t="inlineStr">
         <is>
-          <t>CopySkill</t>
+          <t>PermanentAddFlat</t>
         </is>
       </c>
       <c r="J72" s="0" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K72" s="0" t="inlineStr">
         <is>
-          <t>从来源作用域随机复制actionCount个技能给目标</t>
+          <t>目标永久加法+X(跨结算持久)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="H73" s="0" t="inlineStr">
         <is>
-          <t>TempCopyDish</t>
+          <t>PermanentAddMult</t>
         </is>
       </c>
       <c r="J73" s="0" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K73" s="0" t="inlineStr">
         <is>
-          <t>临时复制目标菜到空格(本次品鉴)</t>
+          <t>目标永久乘区*X(跨结算持久)</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="E74" s="0" t="n"/>
-      <c r="F74" s="0" t="n"/>
-      <c r="G74" s="0" t="n"/>
       <c r="H74" s="0" t="inlineStr">
         <is>
-          <t>TriggerSweetTransfer</t>
+          <t>AddCountAs</t>
         </is>
       </c>
       <c r="J74" s="0" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K74" s="0" t="inlineStr">
         <is>
-          <t>触发作用域内食物各执行一次自身甜蜜传递</t>
+          <t>目标"视为食物数"+X*count</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="0" t="inlineStr">
-        <is>
-          <t>SkillTrigger</t>
-        </is>
-      </c>
-      <c r="C75" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D75" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F75" s="0" t="inlineStr">
-        <is>
-          <t>技能触发时机</t>
-        </is>
-      </c>
       <c r="H75" s="0" t="inlineStr">
         <is>
-          <t>OnSettle</t>
+          <t>CopySkill</t>
         </is>
       </c>
       <c r="J75" s="0" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K75" s="0" t="inlineStr">
         <is>
-          <t>结算时</t>
+          <t>从来源作用域随机复制actionCount个技能给目标</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="H76" s="0" t="inlineStr">
         <is>
+          <t>TempCopyDish</t>
+        </is>
+      </c>
+      <c r="J76" s="0" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K76" s="0" t="inlineStr">
+        <is>
+          <t>临时复制目标菜到空格(本次品鉴)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="E77" s="0" t="n"/>
+      <c r="F77" s="0" t="n"/>
+      <c r="G77" s="0" t="n"/>
+      <c r="H77" s="0" t="inlineStr">
+        <is>
+          <t>TriggerSweetTransfer</t>
+        </is>
+      </c>
+      <c r="J77" s="0" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K77" s="0" t="inlineStr">
+        <is>
+          <t>触发作用域内食物各执行一次自身甜蜜传递</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>SkillTrigger</t>
+        </is>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F78" s="0" t="inlineStr">
+        <is>
+          <t>技能触发时机</t>
+        </is>
+      </c>
+      <c r="H78" s="0" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="J78" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K78" s="0" t="inlineStr">
+        <is>
+          <t>结算时</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="H79" s="0" t="inlineStr">
+        <is>
           <t>OnServe</t>
         </is>
       </c>
-      <c r="J76" s="0" t="inlineStr">
+      <c r="J79" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K76" s="0" t="inlineStr">
+      <c r="K79" s="0" t="inlineStr">
         <is>
           <t>上菜时</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" t="inlineStr">
+    <row r="80">
+      <c r="B80" s="0" t="inlineStr">
         <is>
           <t>MaterialEffectType</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C80" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D80" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F80" s="0" t="inlineStr">
         <is>
           <t>餐桌材质效果类型</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H80" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J77" t="n">
+      <c r="J80" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K80" s="0" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="H78" t="inlineStr">
+    <row r="81">
+      <c r="H81" s="0" t="inlineStr">
         <is>
           <t>AddFlat</t>
         </is>
       </c>
-      <c r="J78" t="n">
+      <c r="J81" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="K81" s="0" t="inlineStr">
         <is>
           <t>分数+值(临时,樱桃木)</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="H79" t="inlineStr">
+    <row r="82">
+      <c r="H82" s="0" t="inlineStr">
         <is>
           <t>PermanentAddFlat</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="J82" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K82" s="0" t="inlineStr">
         <is>
           <t>分数永久+值(胡桃木)</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="H80" t="inlineStr">
+    <row r="83">
+      <c r="H83" s="0" t="inlineStr">
         <is>
           <t>AddMultFlat</t>
         </is>
       </c>
-      <c r="J80" t="n">
+      <c r="J83" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K83" s="0" t="inlineStr">
         <is>
           <t>倍率+值(临时,大理石)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="H81" t="inlineStr">
+    <row r="84">
+      <c r="H84" s="0" t="inlineStr">
         <is>
           <t>AddMult</t>
         </is>
       </c>
-      <c r="J81" t="n">
+      <c r="J84" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K84" s="0" t="inlineStr">
         <is>
           <t>倍率×值(黑曜石)</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="H82" t="inlineStr">
+    <row r="85">
+      <c r="H85" s="0" t="inlineStr">
         <is>
           <t>AddMultFlatPerCell</t>
         </is>
       </c>
-      <c r="J82" t="n">
+      <c r="J85" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="K85" s="0" t="inlineStr">
         <is>
           <t>每占1格本材质倍率+值(翡翠)</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="H83" t="inlineStr">
+    <row r="86">
+      <c r="H86" s="0" t="inlineStr">
         <is>
           <t>GrantGoldIfCellCount</t>
         </is>
       </c>
-      <c r="J83" t="n">
+      <c r="J86" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K86" s="0" t="inlineStr">
         <is>
           <t>占&gt;=阈值格获得金币(金)</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="H84" t="inlineStr">
+    <row r="87">
+      <c r="H87" s="0" t="inlineStr">
         <is>
           <t>GrantItemRollIfCellCount</t>
         </is>
       </c>
-      <c r="J84" t="n">
+      <c r="J87" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="K87" s="0" t="inlineStr">
         <is>
           <t>占&gt;=阈值格1/3获得主动道具(银)</t>
         </is>
